--- a/ROSA_vitaSPEC/Results/test_pretraitements/ratio.alpha.natif/Resultats_ratio.alpha.natif_moy_R2.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/ratio.alpha.natif/Resultats_ratio.alpha.natif_moy_R2.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P47"/>
+  <dimension ref="A1:Q43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -362,75 +362,80 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>LV0_R2</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>LV1_R2</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>LV2_R2</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>LV3_R2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>LV4_R2</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>LV5_R2</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>LV6_R2</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>LV7_R2</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>LV8_R2</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>LV9_R2</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>LV10_R2</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>LV11_R2</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>LV12_R2</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>LV13_R2</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>LV14_R2</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>LV15_R2</t>
         </is>
@@ -443,48 +448,51 @@
         </is>
       </c>
       <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
         <v>0.002723038929463795</v>
       </c>
-      <c r="C2">
+      <c r="D2">
         <v>0.01973441721868208</v>
       </c>
-      <c r="D2">
+      <c r="E2">
         <v>0.04378066166732242</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>0.06096862202739972</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>0.09599601572450545</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>0.173778372340852</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>0.223485559008283</v>
       </c>
-      <c r="I2">
+      <c r="J2">
         <v>0.3173262258441522</v>
       </c>
-      <c r="J2">
+      <c r="K2">
         <v>0.3735979408159634</v>
       </c>
-      <c r="K2">
+      <c r="L2">
         <v>0.413131765370821</v>
       </c>
-      <c r="L2">
+      <c r="M2">
         <v>0.5318822522833975</v>
       </c>
-      <c r="M2">
+      <c r="N2">
         <v>0.5917948210725603</v>
       </c>
-      <c r="N2">
+      <c r="O2">
         <v>0.6895138164027349</v>
       </c>
-      <c r="O2">
+      <c r="P2">
         <v>0.7624334950628289</v>
       </c>
-      <c r="P2">
+      <c r="Q2">
         <v>0.7876400751453198</v>
       </c>
     </row>
@@ -495,48 +503,51 @@
         </is>
       </c>
       <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
         <v>0.03351742271212166</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>0.1651601529804764</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>0.3007881657654894</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>0.3508660045516101</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>0.4295092641482666</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>0.495580985626306</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>0.589659847417956</v>
       </c>
-      <c r="I3">
+      <c r="J3">
         <v>0.6444911911449196</v>
       </c>
-      <c r="J3">
+      <c r="K3">
         <v>0.6915937050876377</v>
       </c>
-      <c r="K3">
+      <c r="L3">
         <v>0.7310154767967854</v>
       </c>
-      <c r="L3">
+      <c r="M3">
         <v>0.7555573606421353</v>
       </c>
-      <c r="M3">
+      <c r="N3">
         <v>0.7920122153232129</v>
       </c>
-      <c r="N3">
+      <c r="O3">
         <v>0.8269708736323308</v>
       </c>
-      <c r="O3">
+      <c r="P3">
         <v>0.8668947562022491</v>
       </c>
-      <c r="P3">
+      <c r="Q3">
         <v>0.8844109465629831</v>
       </c>
     </row>
@@ -547,48 +558,51 @@
         </is>
       </c>
       <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
         <v>0.002095491878692846</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>0.005773563953130223</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>0.02995847307089206</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>0.04529767877313995</v>
       </c>
-      <c r="F4">
+      <c r="G4">
         <v>0.1513246342190704</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>0.2337936646036769</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>0.2989266230427343</v>
       </c>
-      <c r="I4">
+      <c r="J4">
         <v>0.4117475153382458</v>
       </c>
-      <c r="J4">
+      <c r="K4">
         <v>0.4600814241117216</v>
       </c>
-      <c r="K4">
+      <c r="L4">
         <v>0.5638023432139938</v>
       </c>
-      <c r="L4">
+      <c r="M4">
         <v>0.6463744226939652</v>
       </c>
-      <c r="M4">
+      <c r="N4">
         <v>0.7058547079011699</v>
       </c>
-      <c r="N4">
+      <c r="O4">
         <v>0.7414169505238954</v>
       </c>
-      <c r="O4">
+      <c r="P4">
         <v>0.7585413447559489</v>
       </c>
-      <c r="P4">
+      <c r="Q4">
         <v>0.7786824043173382</v>
       </c>
     </row>
@@ -599,48 +613,51 @@
         </is>
       </c>
       <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
         <v>0.009423747151691142</v>
       </c>
-      <c r="C5">
+      <c r="D5">
         <v>0.06192592747206072</v>
       </c>
-      <c r="D5">
+      <c r="E5">
         <v>0.1526000152306397</v>
       </c>
-      <c r="E5">
+      <c r="F5">
         <v>0.3005112577498246</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>0.3712997523571637</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>0.5233057261512912</v>
       </c>
-      <c r="H5">
+      <c r="I5">
         <v>0.5666279716496452</v>
       </c>
-      <c r="I5">
+      <c r="J5">
         <v>0.6379070710961903</v>
       </c>
-      <c r="J5">
+      <c r="K5">
         <v>0.6743178092460316</v>
       </c>
-      <c r="K5">
+      <c r="L5">
         <v>0.7045300990826819</v>
       </c>
-      <c r="L5">
+      <c r="M5">
         <v>0.7465621926041082</v>
       </c>
-      <c r="M5">
+      <c r="N5">
         <v>0.7673024823816378</v>
       </c>
-      <c r="N5">
+      <c r="O5">
         <v>0.7924209566584711</v>
       </c>
-      <c r="O5">
+      <c r="P5">
         <v>0.8077856248319031</v>
       </c>
-      <c r="P5">
+      <c r="Q5">
         <v>0.8308395635648822</v>
       </c>
     </row>
@@ -651,48 +668,51 @@
         </is>
       </c>
       <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
         <v>0.006391824904337318</v>
       </c>
-      <c r="C6">
+      <c r="D6">
         <v>0.05720736647241975</v>
       </c>
-      <c r="D6">
+      <c r="E6">
         <v>0.11190502323249</v>
       </c>
-      <c r="E6">
+      <c r="F6">
         <v>0.3370605025616141</v>
       </c>
-      <c r="F6">
+      <c r="G6">
         <v>0.4063124270033294</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>0.5386239156826438</v>
       </c>
-      <c r="H6">
+      <c r="I6">
         <v>0.5938288985303577</v>
       </c>
-      <c r="I6">
+      <c r="J6">
         <v>0.6252085997883606</v>
       </c>
-      <c r="J6">
+      <c r="K6">
         <v>0.6688330515085401</v>
       </c>
-      <c r="K6">
+      <c r="L6">
         <v>0.6941781486820762</v>
       </c>
-      <c r="L6">
+      <c r="M6">
         <v>0.7355253286128063</v>
       </c>
-      <c r="M6">
+      <c r="N6">
         <v>0.7613817206142862</v>
       </c>
-      <c r="N6">
+      <c r="O6">
         <v>0.7841144919581982</v>
       </c>
-      <c r="O6">
+      <c r="P6">
         <v>0.8017134998319826</v>
       </c>
-      <c r="P6">
+      <c r="Q6">
         <v>0.8271192773773713</v>
       </c>
     </row>
@@ -703,48 +723,51 @@
         </is>
       </c>
       <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
         <v>0.002192969171317283</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>0.006588965462423158</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>0.02035677996657081</v>
       </c>
-      <c r="E7">
+      <c r="F7">
         <v>0.03795988853451182</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <v>0.09667505266163368</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>0.1922853986878715</v>
       </c>
-      <c r="H7">
+      <c r="I7">
         <v>0.27398641082883</v>
       </c>
-      <c r="I7">
+      <c r="J7">
         <v>0.3327209678472625</v>
       </c>
-      <c r="J7">
+      <c r="K7">
         <v>0.4294938265718885</v>
       </c>
-      <c r="K7">
+      <c r="L7">
         <v>0.4865550180130205</v>
       </c>
-      <c r="L7">
+      <c r="M7">
         <v>0.6140266298929516</v>
       </c>
-      <c r="M7">
+      <c r="N7">
         <v>0.7095197156826177</v>
       </c>
-      <c r="N7">
+      <c r="O7">
         <v>0.72725201467658</v>
       </c>
-      <c r="O7">
+      <c r="P7">
         <v>0.7628594883990689</v>
       </c>
-      <c r="P7">
+      <c r="Q7">
         <v>0.7882271155653908</v>
       </c>
     </row>
@@ -755,48 +778,51 @@
         </is>
       </c>
       <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
         <v>0.003084993111214129</v>
       </c>
-      <c r="C8">
+      <c r="D8">
         <v>0.006360608502831488</v>
       </c>
-      <c r="D8">
+      <c r="E8">
         <v>0.03266112381237796</v>
       </c>
-      <c r="E8">
+      <c r="F8">
         <v>0.1470178435082368</v>
       </c>
-      <c r="F8">
+      <c r="G8">
         <v>0.2009409360953301</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>0.2780851945667606</v>
       </c>
-      <c r="H8">
+      <c r="I8">
         <v>0.3313311850833552</v>
       </c>
-      <c r="I8">
+      <c r="J8">
         <v>0.4542921482793524</v>
       </c>
-      <c r="J8">
+      <c r="K8">
         <v>0.504991366387052</v>
       </c>
-      <c r="K8">
+      <c r="L8">
         <v>0.6422090364131852</v>
       </c>
-      <c r="L8">
+      <c r="M8">
         <v>0.6819604146281788</v>
       </c>
-      <c r="M8">
+      <c r="N8">
         <v>0.7243891810334775</v>
       </c>
-      <c r="N8">
+      <c r="O8">
         <v>0.7438862149845313</v>
       </c>
-      <c r="O8">
+      <c r="P8">
         <v>0.760377240033506</v>
       </c>
-      <c r="P8">
+      <c r="Q8">
         <v>0.7780313044146675</v>
       </c>
     </row>
@@ -807,48 +833,51 @@
         </is>
       </c>
       <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
         <v>0.003066166589238639</v>
       </c>
-      <c r="C9">
+      <c r="D9">
         <v>0.006171733526849299</v>
       </c>
-      <c r="D9">
+      <c r="E9">
         <v>0.02961106150415649</v>
       </c>
-      <c r="E9">
+      <c r="F9">
         <v>0.1282665703860598</v>
       </c>
-      <c r="F9">
+      <c r="G9">
         <v>0.1745370557434528</v>
       </c>
-      <c r="G9">
+      <c r="H9">
         <v>0.2395523241635192</v>
       </c>
-      <c r="H9">
+      <c r="I9">
         <v>0.2806916154506327</v>
       </c>
-      <c r="I9">
+      <c r="J9">
         <v>0.3833290563600694</v>
       </c>
-      <c r="J9">
+      <c r="K9">
         <v>0.4176439893691496</v>
       </c>
-      <c r="K9">
+      <c r="L9">
         <v>0.5760472650059768</v>
       </c>
-      <c r="L9">
+      <c r="M9">
         <v>0.6082409274536564</v>
       </c>
-      <c r="M9">
+      <c r="N9">
         <v>0.6249777762732516</v>
       </c>
-      <c r="N9">
+      <c r="O9">
         <v>0.656092904448762</v>
       </c>
-      <c r="O9">
+      <c r="P9">
         <v>0.6661907029640373</v>
       </c>
-      <c r="P9">
+      <c r="Q9">
         <v>0.6851375389649275</v>
       </c>
     </row>
@@ -859,48 +888,51 @@
         </is>
       </c>
       <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
         <v>0.003066052436127897</v>
       </c>
-      <c r="C10">
+      <c r="D10">
         <v>0.006171782479068244</v>
       </c>
-      <c r="D10">
+      <c r="E10">
         <v>0.02969097725713499</v>
       </c>
-      <c r="E10">
+      <c r="F10">
         <v>0.1279116286493694</v>
       </c>
-      <c r="F10">
+      <c r="G10">
         <v>0.1738890554771397</v>
       </c>
-      <c r="G10">
+      <c r="H10">
         <v>0.2392688590283856</v>
       </c>
-      <c r="H10">
+      <c r="I10">
         <v>0.2794468932548898</v>
       </c>
-      <c r="I10">
+      <c r="J10">
         <v>0.3799918596719714</v>
       </c>
-      <c r="J10">
+      <c r="K10">
         <v>0.4133951133504453</v>
       </c>
-      <c r="K10">
+      <c r="L10">
         <v>0.5674978373626196</v>
       </c>
-      <c r="L10">
+      <c r="M10">
         <v>0.6002784243010217</v>
       </c>
-      <c r="M10">
+      <c r="N10">
         <v>0.6141870796803695</v>
       </c>
-      <c r="N10">
+      <c r="O10">
         <v>0.6425314762477428</v>
       </c>
-      <c r="O10">
+      <c r="P10">
         <v>0.6542849896912222</v>
       </c>
-      <c r="P10">
+      <c r="Q10">
         <v>0.6725681236371652</v>
       </c>
     </row>
@@ -911,48 +943,51 @@
         </is>
       </c>
       <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11">
         <v>0.003070895938557805</v>
       </c>
-      <c r="C11">
+      <c r="D11">
         <v>0.006213113683565918</v>
       </c>
-      <c r="D11">
+      <c r="E11">
         <v>0.03004412528198708</v>
       </c>
-      <c r="E11">
+      <c r="F11">
         <v>0.126000783100542</v>
       </c>
-      <c r="F11">
+      <c r="G11">
         <v>0.1704197676557629</v>
       </c>
-      <c r="G11">
+      <c r="H11">
         <v>0.2355913012721843</v>
       </c>
-      <c r="H11">
+      <c r="I11">
         <v>0.2771197810621415</v>
       </c>
-      <c r="I11">
+      <c r="J11">
         <v>0.3824472836581628</v>
       </c>
-      <c r="J11">
+      <c r="K11">
         <v>0.4202423136326927</v>
       </c>
-      <c r="K11">
+      <c r="L11">
         <v>0.5721033339573751</v>
       </c>
-      <c r="L11">
+      <c r="M11">
         <v>0.6052276285880624</v>
       </c>
-      <c r="M11">
+      <c r="N11">
         <v>0.6276795952289511</v>
       </c>
-      <c r="N11">
+      <c r="O11">
         <v>0.6511627230397445</v>
       </c>
-      <c r="O11">
+      <c r="P11">
         <v>0.6694578449043324</v>
       </c>
-      <c r="P11">
+      <c r="Q11">
         <v>0.6803492510249505</v>
       </c>
     </row>
@@ -963,48 +998,51 @@
         </is>
       </c>
       <c r="B12">
+        <v>0</v>
+      </c>
+      <c r="C12">
         <v>0.00984539776587734</v>
       </c>
-      <c r="C12">
+      <c r="D12">
         <v>0.06218273943922425</v>
       </c>
-      <c r="D12">
+      <c r="E12">
         <v>0.1524420919292414</v>
       </c>
-      <c r="E12">
+      <c r="F12">
         <v>0.2582927610929162</v>
       </c>
-      <c r="F12">
+      <c r="G12">
         <v>0.3933484538278633</v>
       </c>
-      <c r="G12">
+      <c r="H12">
         <v>0.5365660355674025</v>
       </c>
-      <c r="H12">
+      <c r="I12">
         <v>0.5739375602721897</v>
       </c>
-      <c r="I12">
+      <c r="J12">
         <v>0.6469435270516593</v>
       </c>
-      <c r="J12">
+      <c r="K12">
         <v>0.6843535153341735</v>
       </c>
-      <c r="K12">
+      <c r="L12">
         <v>0.7119793826809635</v>
       </c>
-      <c r="L12">
+      <c r="M12">
         <v>0.7558651062096575</v>
       </c>
-      <c r="M12">
+      <c r="N12">
         <v>0.7756597881136078</v>
       </c>
-      <c r="N12">
+      <c r="O12">
         <v>0.7974163852546744</v>
       </c>
-      <c r="O12">
+      <c r="P12">
         <v>0.809740122271099</v>
       </c>
-      <c r="P12">
+      <c r="Q12">
         <v>0.8366793768670422</v>
       </c>
     </row>
@@ -1015,48 +1053,51 @@
         </is>
       </c>
       <c r="B13">
+        <v>0</v>
+      </c>
+      <c r="C13">
         <v>0.01347154639938863</v>
       </c>
-      <c r="C13">
+      <c r="D13">
         <v>0.1081460933098918</v>
       </c>
-      <c r="D13">
+      <c r="E13">
         <v>0.1794170517436119</v>
       </c>
-      <c r="E13">
+      <c r="F13">
         <v>0.2789226145040475</v>
       </c>
-      <c r="F13">
+      <c r="G13">
         <v>0.328116413017392</v>
       </c>
-      <c r="G13">
+      <c r="H13">
         <v>0.4506659140426592</v>
       </c>
-      <c r="H13">
+      <c r="I13">
         <v>0.5412971384227425</v>
       </c>
-      <c r="I13">
+      <c r="J13">
         <v>0.5982299128686911</v>
       </c>
-      <c r="J13">
+      <c r="K13">
         <v>0.6635100269236764</v>
       </c>
-      <c r="K13">
+      <c r="L13">
         <v>0.7146494437797578</v>
       </c>
-      <c r="L13">
+      <c r="M13">
         <v>0.7362616720577615</v>
       </c>
-      <c r="M13">
+      <c r="N13">
         <v>0.7714399967903849</v>
       </c>
-      <c r="N13">
+      <c r="O13">
         <v>0.7837641195752013</v>
       </c>
-      <c r="O13">
+      <c r="P13">
         <v>0.8048373777044596</v>
       </c>
-      <c r="P13">
+      <c r="Q13">
         <v>0.8227299791943359</v>
       </c>
     </row>
@@ -1067,48 +1108,51 @@
         </is>
       </c>
       <c r="B14">
+        <v>0</v>
+      </c>
+      <c r="C14">
         <v>0.002187363093658301</v>
       </c>
-      <c r="C14">
+      <c r="D14">
         <v>0.006528706576494736</v>
       </c>
-      <c r="D14">
+      <c r="E14">
         <v>0.01956895164989447</v>
       </c>
-      <c r="E14">
+      <c r="F14">
         <v>0.03571908307092619</v>
       </c>
-      <c r="F14">
+      <c r="G14">
         <v>0.0884525186190247</v>
       </c>
-      <c r="G14">
+      <c r="H14">
         <v>0.1714661962069944</v>
       </c>
-      <c r="H14">
+      <c r="I14">
         <v>0.2414388019133221</v>
       </c>
-      <c r="I14">
+      <c r="J14">
         <v>0.2869332363363716</v>
       </c>
-      <c r="J14">
+      <c r="K14">
         <v>0.372680496099896</v>
       </c>
-      <c r="K14">
+      <c r="L14">
         <v>0.4300039395737948</v>
       </c>
-      <c r="L14">
+      <c r="M14">
         <v>0.5419043639948788</v>
       </c>
-      <c r="M14">
+      <c r="N14">
         <v>0.6445195478868793</v>
       </c>
-      <c r="N14">
+      <c r="O14">
         <v>0.66317860262355</v>
       </c>
-      <c r="O14">
+      <c r="P14">
         <v>0.6979952472832345</v>
       </c>
-      <c r="P14">
+      <c r="Q14">
         <v>0.7202304438856904</v>
       </c>
     </row>
@@ -1119,48 +1163,51 @@
         </is>
       </c>
       <c r="B15">
+        <v>0</v>
+      </c>
+      <c r="C15">
         <v>0.002184750180993511</v>
       </c>
-      <c r="C15">
+      <c r="D15">
         <v>0.006505803748539152</v>
       </c>
-      <c r="D15">
+      <c r="E15">
         <v>0.01927876234891091</v>
       </c>
-      <c r="E15">
+      <c r="F15">
         <v>0.03487073172658084</v>
       </c>
-      <c r="F15">
+      <c r="G15">
         <v>0.08519691033280385</v>
       </c>
-      <c r="G15">
+      <c r="H15">
         <v>0.1644948214719177</v>
       </c>
-      <c r="H15">
+      <c r="I15">
         <v>0.2323261548406772</v>
       </c>
-      <c r="I15">
+      <c r="J15">
         <v>0.2761882116831534</v>
       </c>
-      <c r="J15">
+      <c r="K15">
         <v>0.3575338940302838</v>
       </c>
-      <c r="K15">
+      <c r="L15">
         <v>0.4152982292260284</v>
       </c>
-      <c r="L15">
+      <c r="M15">
         <v>0.5197393975362143</v>
       </c>
-      <c r="M15">
+      <c r="N15">
         <v>0.6184069269358634</v>
       </c>
-      <c r="N15">
+      <c r="O15">
         <v>0.6352315661203434</v>
       </c>
-      <c r="O15">
+      <c r="P15">
         <v>0.666603250018373</v>
       </c>
-      <c r="P15">
+      <c r="Q15">
         <v>0.6893895636240461</v>
       </c>
     </row>
@@ -1171,48 +1218,51 @@
         </is>
       </c>
       <c r="B16">
+        <v>0</v>
+      </c>
+      <c r="C16">
         <v>0.00218201239509197</v>
       </c>
-      <c r="C16">
+      <c r="D16">
         <v>0.00648291618011998</v>
       </c>
-      <c r="D16">
+      <c r="E16">
         <v>0.01902651316653914</v>
       </c>
-      <c r="E16">
+      <c r="F16">
         <v>0.03427142652479132</v>
       </c>
-      <c r="F16">
+      <c r="G16">
         <v>0.08389368193972024</v>
       </c>
-      <c r="G16">
+      <c r="H16">
         <v>0.1634907151662891</v>
       </c>
-      <c r="H16">
+      <c r="I16">
         <v>0.231324072779751</v>
       </c>
-      <c r="I16">
+      <c r="J16">
         <v>0.2737931770978297</v>
       </c>
-      <c r="J16">
+      <c r="K16">
         <v>0.352670771778773</v>
       </c>
-      <c r="K16">
+      <c r="L16">
         <v>0.4099353685489241</v>
       </c>
-      <c r="L16">
+      <c r="M16">
         <v>0.5144321513927517</v>
       </c>
-      <c r="M16">
+      <c r="N16">
         <v>0.6135408599583435</v>
       </c>
-      <c r="N16">
+      <c r="O16">
         <v>0.6333625530874599</v>
       </c>
-      <c r="O16">
+      <c r="P16">
         <v>0.6676480186268192</v>
       </c>
-      <c r="P16">
+      <c r="Q16">
         <v>0.6906440275191158</v>
       </c>
     </row>
@@ -1223,48 +1273,51 @@
         </is>
       </c>
       <c r="B17">
+        <v>0</v>
+      </c>
+      <c r="C17">
         <v>0.002181023368567736</v>
       </c>
-      <c r="C17">
+      <c r="D17">
         <v>0.006482689457453339</v>
       </c>
-      <c r="D17">
+      <c r="E17">
         <v>0.01901532607016454</v>
       </c>
-      <c r="E17">
+      <c r="F17">
         <v>0.03416148814200126</v>
       </c>
-      <c r="F17">
+      <c r="G17">
         <v>0.08267166417946703</v>
       </c>
-      <c r="G17">
+      <c r="H17">
         <v>0.1608599713024388</v>
       </c>
-      <c r="H17">
+      <c r="I17">
         <v>0.2288566383174261</v>
       </c>
-      <c r="I17">
+      <c r="J17">
         <v>0.267472466748816</v>
       </c>
-      <c r="J17">
+      <c r="K17">
         <v>0.3408594503828023</v>
       </c>
-      <c r="K17">
+      <c r="L17">
         <v>0.3983581195114867</v>
       </c>
-      <c r="L17">
+      <c r="M17">
         <v>0.4989695939401546</v>
       </c>
-      <c r="M17">
+      <c r="N17">
         <v>0.5868480513604215</v>
       </c>
-      <c r="N17">
+      <c r="O17">
         <v>0.6123294722154634</v>
       </c>
-      <c r="O17">
+      <c r="P17">
         <v>0.6507623350340451</v>
       </c>
-      <c r="P17">
+      <c r="Q17">
         <v>0.6729150774276178</v>
       </c>
     </row>
@@ -1275,48 +1328,51 @@
         </is>
       </c>
       <c r="B18">
+        <v>0</v>
+      </c>
+      <c r="C18">
         <v>0.009803218541614034</v>
       </c>
-      <c r="C18">
+      <c r="D18">
         <v>0.06169837002995515</v>
       </c>
-      <c r="D18">
+      <c r="E18">
         <v>0.158406641871942</v>
       </c>
-      <c r="E18">
+      <c r="F18">
         <v>0.2695537138208903</v>
       </c>
-      <c r="F18">
+      <c r="G18">
         <v>0.3941643900701847</v>
       </c>
-      <c r="G18">
+      <c r="H18">
         <v>0.5337123934833045</v>
       </c>
-      <c r="H18">
+      <c r="I18">
         <v>0.6545326240451992</v>
       </c>
-      <c r="I18">
+      <c r="J18">
         <v>0.6822244561778159</v>
       </c>
-      <c r="J18">
+      <c r="K18">
         <v>0.697539276972569</v>
       </c>
-      <c r="K18">
+      <c r="L18">
         <v>0.7078021664105191</v>
       </c>
-      <c r="L18">
+      <c r="M18">
         <v>0.7559560711594482</v>
       </c>
-      <c r="M18">
+      <c r="N18">
         <v>0.7765765823540016</v>
       </c>
-      <c r="N18">
+      <c r="O18">
         <v>0.802219541854131</v>
       </c>
-      <c r="O18">
+      <c r="P18">
         <v>0.8245196930282006</v>
       </c>
-      <c r="P18">
+      <c r="Q18">
         <v>0.845226029991788</v>
       </c>
     </row>
@@ -1327,48 +1383,51 @@
         </is>
       </c>
       <c r="B19">
+        <v>0</v>
+      </c>
+      <c r="C19">
         <v>0.006696296304751992</v>
       </c>
-      <c r="C19">
+      <c r="D19">
         <v>0.05674612047356198</v>
       </c>
-      <c r="D19">
+      <c r="E19">
         <v>0.1134700955573794</v>
       </c>
-      <c r="E19">
+      <c r="F19">
         <v>0.3131467719901885</v>
       </c>
-      <c r="F19">
+      <c r="G19">
         <v>0.4130953052871615</v>
       </c>
-      <c r="G19">
+      <c r="H19">
         <v>0.5129727036946912</v>
       </c>
-      <c r="H19">
+      <c r="I19">
         <v>0.5516562592706816</v>
       </c>
-      <c r="I19">
+      <c r="J19">
         <v>0.6186361021718696</v>
       </c>
-      <c r="J19">
+      <c r="K19">
         <v>0.661980250487946</v>
       </c>
-      <c r="K19">
+      <c r="L19">
         <v>0.6937276043508367</v>
       </c>
-      <c r="L19">
+      <c r="M19">
         <v>0.741053305395533</v>
       </c>
-      <c r="M19">
+      <c r="N19">
         <v>0.7674925718573055</v>
       </c>
-      <c r="N19">
+      <c r="O19">
         <v>0.7983174602344907</v>
       </c>
-      <c r="O19">
+      <c r="P19">
         <v>0.8113032239514906</v>
       </c>
-      <c r="P19">
+      <c r="Q19">
         <v>0.8360492624839494</v>
       </c>
     </row>
@@ -1379,48 +1438,51 @@
         </is>
       </c>
       <c r="B20">
+        <v>0</v>
+      </c>
+      <c r="C20">
         <v>0.005936472761896128</v>
       </c>
-      <c r="C20">
+      <c r="D20">
         <v>0.08699080666187731</v>
       </c>
-      <c r="D20">
+      <c r="E20">
         <v>0.1184976617950313</v>
       </c>
-      <c r="E20">
+      <c r="F20">
         <v>0.2402932129064006</v>
       </c>
-      <c r="F20">
+      <c r="G20">
         <v>0.3454446627103117</v>
       </c>
-      <c r="G20">
+      <c r="H20">
         <v>0.4537481357953815</v>
       </c>
-      <c r="H20">
+      <c r="I20">
         <v>0.5046376937142263</v>
       </c>
-      <c r="I20">
+      <c r="J20">
         <v>0.5806443232295002</v>
       </c>
-      <c r="J20">
+      <c r="K20">
         <v>0.6064158624719307</v>
       </c>
-      <c r="K20">
+      <c r="L20">
         <v>0.6740173480015965</v>
       </c>
-      <c r="L20">
+      <c r="M20">
         <v>0.7092175376278333</v>
       </c>
-      <c r="M20">
+      <c r="N20">
         <v>0.7475518778178124</v>
       </c>
-      <c r="N20">
+      <c r="O20">
         <v>0.7673403951597917</v>
       </c>
-      <c r="O20">
+      <c r="P20">
         <v>0.7902657825112627</v>
       </c>
-      <c r="P20">
+      <c r="Q20">
         <v>0.8075618309443635</v>
       </c>
     </row>
@@ -1431,48 +1493,51 @@
         </is>
       </c>
       <c r="B21">
+        <v>0</v>
+      </c>
+      <c r="C21">
         <v>0.03318963886345039</v>
       </c>
-      <c r="C21">
+      <c r="D21">
         <v>0.1513718719406744</v>
       </c>
-      <c r="D21">
+      <c r="E21">
         <v>0.2694098775539364</v>
       </c>
-      <c r="E21">
+      <c r="F21">
         <v>0.3198786767907144</v>
       </c>
-      <c r="F21">
+      <c r="G21">
         <v>0.3845088737130733</v>
       </c>
-      <c r="G21">
+      <c r="H21">
         <v>0.4565913027928286</v>
       </c>
-      <c r="H21">
+      <c r="I21">
         <v>0.5655970071852854</v>
       </c>
-      <c r="I21">
+      <c r="J21">
         <v>0.6381410839842154</v>
       </c>
-      <c r="J21">
+      <c r="K21">
         <v>0.6896095349504346</v>
       </c>
-      <c r="K21">
+      <c r="L21">
         <v>0.735865948783637</v>
       </c>
-      <c r="L21">
+      <c r="M21">
         <v>0.7678969898517907</v>
       </c>
-      <c r="M21">
+      <c r="N21">
         <v>0.7952508376541699</v>
       </c>
-      <c r="N21">
+      <c r="O21">
         <v>0.8261536139736422</v>
       </c>
-      <c r="O21">
+      <c r="P21">
         <v>0.8651579420279286</v>
       </c>
-      <c r="P21">
+      <c r="Q21">
         <v>0.8844620804460707</v>
       </c>
     </row>
@@ -1483,48 +1548,51 @@
         </is>
       </c>
       <c r="B22">
+        <v>0</v>
+      </c>
+      <c r="C22">
         <v>0.03318976526592121</v>
       </c>
-      <c r="C22">
+      <c r="D22">
         <v>0.1533655433418711</v>
       </c>
-      <c r="D22">
+      <c r="E22">
         <v>0.2673969854450983</v>
       </c>
-      <c r="E22">
+      <c r="F22">
         <v>0.3167968360535747</v>
       </c>
-      <c r="F22">
+      <c r="G22">
         <v>0.376982101030669</v>
       </c>
-      <c r="G22">
+      <c r="H22">
         <v>0.4410262248379588</v>
       </c>
-      <c r="H22">
+      <c r="I22">
         <v>0.545765275980497</v>
       </c>
-      <c r="I22">
+      <c r="J22">
         <v>0.6136371112573702</v>
       </c>
-      <c r="J22">
+      <c r="K22">
         <v>0.6715141754230696</v>
       </c>
-      <c r="K22">
+      <c r="L22">
         <v>0.7214820723999809</v>
       </c>
-      <c r="L22">
+      <c r="M22">
         <v>0.7694804396751316</v>
       </c>
-      <c r="M22">
+      <c r="N22">
         <v>0.8021745249785589</v>
       </c>
-      <c r="N22">
+      <c r="O22">
         <v>0.8363609499219067</v>
       </c>
-      <c r="O22">
+      <c r="P22">
         <v>0.8566212985723051</v>
       </c>
-      <c r="P22">
+      <c r="Q22">
         <v>0.8740571781534671</v>
       </c>
     </row>
@@ -1535,1296 +1603,1151 @@
         </is>
       </c>
       <c r="B23">
+        <v>0</v>
+      </c>
+      <c r="C23">
         <v>0.01160257680067101</v>
       </c>
-      <c r="C23">
+      <c r="D23">
         <v>0.1148183384090452</v>
       </c>
-      <c r="D23">
+      <c r="E23">
         <v>0.2418588938403936</v>
       </c>
-      <c r="E23">
+      <c r="F23">
         <v>0.2930160887592864</v>
       </c>
-      <c r="F23">
+      <c r="G23">
         <v>0.507321498136958</v>
       </c>
-      <c r="G23">
+      <c r="H23">
         <v>0.5910784628878338</v>
       </c>
-      <c r="H23">
+      <c r="I23">
         <v>0.6414617965287909</v>
       </c>
-      <c r="I23">
+      <c r="J23">
         <v>0.7022572477432897</v>
       </c>
-      <c r="J23">
+      <c r="K23">
         <v>0.74118388288634</v>
       </c>
-      <c r="K23">
+      <c r="L23">
         <v>0.8005558681303501</v>
       </c>
-      <c r="L23">
+      <c r="M23">
         <v>0.8300468216043996</v>
       </c>
-      <c r="M23">
+      <c r="N23">
         <v>0.876189607447775</v>
       </c>
-      <c r="N23">
+      <c r="O23">
         <v>0.8920389964162021</v>
       </c>
-      <c r="O23">
+      <c r="P23">
         <v>0.9053216905461392</v>
       </c>
-      <c r="P23">
+      <c r="Q23">
         <v>0.9212634585050092</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>adj_red_c(950,20,1)_snv_sder_c(1,3,15)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
         </is>
       </c>
       <c r="B24">
-        <v>0.06636227864244038</v>
+        <v>0</v>
       </c>
       <c r="C24">
-        <v>0.1449500796043404</v>
+        <v>0.002408526164219937</v>
       </c>
       <c r="D24">
-        <v>0.2570689858245557</v>
+        <v>0.008757276027620664</v>
       </c>
       <c r="E24">
-        <v>0.283610775396086</v>
+        <v>0.04474539628632446</v>
       </c>
       <c r="F24">
-        <v>0.3594014191333947</v>
+        <v>0.07725856554591481</v>
       </c>
       <c r="G24">
-        <v>0.496702384939787</v>
+        <v>0.110952364780638</v>
       </c>
       <c r="H24">
-        <v>0.5312905926876199</v>
+        <v>0.1543517085940515</v>
       </c>
       <c r="I24">
-        <v>0.594071889328829</v>
+        <v>0.193428886647803</v>
       </c>
       <c r="J24">
-        <v>0.629003294893256</v>
+        <v>0.3867295124123694</v>
       </c>
       <c r="K24">
-        <v>0.6841017149737247</v>
+        <v>0.5612444288772911</v>
       </c>
       <c r="L24">
-        <v>0.7063691880082703</v>
+        <v>0.656332464129622</v>
       </c>
       <c r="M24">
-        <v>0.7481868399189596</v>
+        <v>0.705064733733153</v>
       </c>
       <c r="N24">
-        <v>0.7820038090884005</v>
+        <v>0.7760206709891151</v>
       </c>
       <c r="O24">
-        <v>0.8111125951348979</v>
+        <v>0.824863279741944</v>
       </c>
       <c r="P24">
-        <v>0.8421998337196454</v>
+        <v>0.8455384416494165</v>
+      </c>
+      <c r="Q24">
+        <v>0.8720634734660421</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>adj_red_c(950,20,1)_snv_sder_c(2,3,15)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
         </is>
       </c>
       <c r="B25">
-        <v>0.08439057505495684</v>
+        <v>0</v>
       </c>
       <c r="C25">
-        <v>0.2460751657932647</v>
+        <v>0.002714603445934216</v>
       </c>
       <c r="D25">
-        <v>0.2868473219114945</v>
+        <v>0.01077488566975382</v>
       </c>
       <c r="E25">
-        <v>0.3223059817957918</v>
+        <v>0.05665401111206148</v>
       </c>
       <c r="F25">
-        <v>0.4747967175918885</v>
+        <v>0.09324114524634719</v>
       </c>
       <c r="G25">
-        <v>0.5268719372586654</v>
+        <v>0.103491323820799</v>
       </c>
       <c r="H25">
-        <v>0.5800030827569135</v>
+        <v>0.1513160196174929</v>
       </c>
       <c r="I25">
-        <v>0.6459629999735108</v>
+        <v>0.3459851871550557</v>
       </c>
       <c r="J25">
-        <v>0.6732048881129713</v>
+        <v>0.3928858823728993</v>
       </c>
       <c r="K25">
-        <v>0.7216188557590011</v>
+        <v>0.4637996766635993</v>
       </c>
       <c r="L25">
-        <v>0.7544404559384423</v>
+        <v>0.648040343832438</v>
       </c>
       <c r="M25">
-        <v>0.794542287663965</v>
+        <v>0.6807087651262778</v>
       </c>
       <c r="N25">
-        <v>0.8243412377957376</v>
+        <v>0.7338765257019793</v>
       </c>
       <c r="O25">
-        <v>0.8535123655170987</v>
+        <v>0.7867964588803754</v>
       </c>
       <c r="P25">
-        <v>0.8716543363104954</v>
+        <v>0.8287006191333453</v>
+      </c>
+      <c r="Q25">
+        <v>0.8495537779724189</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>adj_red_c(950,750,1)_snv_sder_c(1,3,15)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
         </is>
       </c>
       <c r="B26">
-        <v>0.03139055198851481</v>
+        <v>0</v>
       </c>
       <c r="C26">
-        <v>0.1234527205802979</v>
+        <v>0.009379657425210297</v>
       </c>
       <c r="D26">
-        <v>0.1757332725669044</v>
+        <v>0.0193453642100857</v>
       </c>
       <c r="E26">
-        <v>0.2098494192843925</v>
+        <v>0.05409405756167451</v>
       </c>
       <c r="F26">
-        <v>0.3290702756952799</v>
+        <v>0.1052627157411438</v>
       </c>
       <c r="G26">
-        <v>0.3714377531593527</v>
+        <v>0.1293365536491764</v>
       </c>
       <c r="H26">
-        <v>0.4103144965741237</v>
+        <v>0.167329671708868</v>
       </c>
       <c r="I26">
-        <v>0.4746938978884087</v>
+        <v>0.3890809299582081</v>
       </c>
       <c r="J26">
-        <v>0.5259427622725807</v>
+        <v>0.5606032711693621</v>
       </c>
       <c r="K26">
-        <v>0.6060841849427008</v>
+        <v>0.5954239970409331</v>
       </c>
       <c r="L26">
-        <v>0.6282679988178044</v>
+        <v>0.684299342680986</v>
       </c>
       <c r="M26">
-        <v>0.6621455247703489</v>
+        <v>0.7356773952780695</v>
       </c>
       <c r="N26">
-        <v>0.6943569399622671</v>
+        <v>0.804427680120105</v>
       </c>
       <c r="O26">
-        <v>0.7485681109540265</v>
+        <v>0.8366182265606904</v>
       </c>
       <c r="P26">
-        <v>0.7798490933655718</v>
+        <v>0.8544506633820679</v>
+      </c>
+      <c r="Q26">
+        <v>0.8806313992206468</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>adj_red_c(950,750,1)_snv_sder_c(2,3,15)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
         </is>
       </c>
       <c r="B27">
-        <v>0.04431555970095791</v>
+        <v>0</v>
       </c>
       <c r="C27">
-        <v>0.237982614833682</v>
+        <v>0.008663746054376253</v>
       </c>
       <c r="D27">
-        <v>0.2633444708315668</v>
+        <v>0.01790862727689124</v>
       </c>
       <c r="E27">
-        <v>0.2974053867220798</v>
+        <v>0.04912101592766061</v>
       </c>
       <c r="F27">
-        <v>0.3757258812713813</v>
+        <v>0.08995385948217316</v>
       </c>
       <c r="G27">
-        <v>0.4350686304067292</v>
+        <v>0.1084414796356123</v>
       </c>
       <c r="H27">
-        <v>0.4979040553437407</v>
+        <v>0.1318609985903132</v>
       </c>
       <c r="I27">
-        <v>0.5917698945765175</v>
+        <v>0.2604308968032154</v>
       </c>
       <c r="J27">
-        <v>0.6702075353000099</v>
+        <v>0.3898231669347061</v>
       </c>
       <c r="K27">
-        <v>0.7090766401884498</v>
+        <v>0.4288997636972938</v>
       </c>
       <c r="L27">
-        <v>0.725404391632785</v>
+        <v>0.5422676701469101</v>
       </c>
       <c r="M27">
-        <v>0.7631289069613143</v>
+        <v>0.5830295836208024</v>
       </c>
       <c r="N27">
-        <v>0.7873627766819626</v>
+        <v>0.6641625139608072</v>
       </c>
       <c r="O27">
-        <v>0.8113031971592657</v>
+        <v>0.6835953149612962</v>
       </c>
       <c r="P27">
-        <v>0.8244220638649669</v>
+        <v>0.7006253775788595</v>
+      </c>
+      <c r="Q27">
+        <v>0.7196146874275037</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
         </is>
       </c>
       <c r="B28">
-        <v>0.002408526164219937</v>
+        <v>0</v>
       </c>
       <c r="C28">
-        <v>0.008757276027620664</v>
+        <v>0.002543824757351376</v>
       </c>
       <c r="D28">
-        <v>0.04474539628632446</v>
+        <v>0.009986620336946972</v>
       </c>
       <c r="E28">
-        <v>0.07725856554591481</v>
+        <v>0.05133917070049843</v>
       </c>
       <c r="F28">
-        <v>0.110952364780638</v>
+        <v>0.08069752145753706</v>
       </c>
       <c r="G28">
-        <v>0.1543517085940515</v>
+        <v>0.08850139590244055</v>
       </c>
       <c r="H28">
-        <v>0.193428886647803</v>
+        <v>0.1207676715205502</v>
       </c>
       <c r="I28">
-        <v>0.3867295124123694</v>
+        <v>0.2343030907602058</v>
       </c>
       <c r="J28">
-        <v>0.5612444288772911</v>
+        <v>0.2642238096513811</v>
       </c>
       <c r="K28">
-        <v>0.656332464129622</v>
+        <v>0.3159435952919578</v>
       </c>
       <c r="L28">
-        <v>0.705064733733153</v>
+        <v>0.495970896123344</v>
       </c>
       <c r="M28">
-        <v>0.7760206709891151</v>
+        <v>0.5400096763014913</v>
       </c>
       <c r="N28">
-        <v>0.824863279741944</v>
+        <v>0.5662339999232379</v>
       </c>
       <c r="O28">
-        <v>0.8455384416494165</v>
+        <v>0.6184832194275695</v>
       </c>
       <c r="P28">
-        <v>0.8720634734660421</v>
+        <v>0.6592048267960624</v>
+      </c>
+      <c r="Q28">
+        <v>0.6893994512225363</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
         </is>
       </c>
       <c r="B29">
-        <v>0.002714603445934216</v>
+        <v>0</v>
       </c>
       <c r="C29">
-        <v>0.01077488566975382</v>
+        <v>0.002542672537104607</v>
       </c>
       <c r="D29">
-        <v>0.05665401111206148</v>
+        <v>0.0100285831785174</v>
       </c>
       <c r="E29">
-        <v>0.09324114524634719</v>
+        <v>0.05125561435964099</v>
       </c>
       <c r="F29">
-        <v>0.103491323820799</v>
+        <v>0.08084902466812893</v>
       </c>
       <c r="G29">
-        <v>0.1513160196174929</v>
+        <v>0.08863527390089143</v>
       </c>
       <c r="H29">
-        <v>0.3459851871550557</v>
+        <v>0.1209152033161167</v>
       </c>
       <c r="I29">
-        <v>0.3928858823728993</v>
+        <v>0.22756556642152</v>
       </c>
       <c r="J29">
-        <v>0.4637996766635993</v>
+        <v>0.2604012424915528</v>
       </c>
       <c r="K29">
-        <v>0.648040343832438</v>
+        <v>0.3130840107676994</v>
       </c>
       <c r="L29">
-        <v>0.6807087651262778</v>
+        <v>0.4801808112663148</v>
       </c>
       <c r="M29">
-        <v>0.7338765257019793</v>
+        <v>0.5329007002870112</v>
       </c>
       <c r="N29">
-        <v>0.7867964588803754</v>
+        <v>0.560322615683525</v>
       </c>
       <c r="O29">
-        <v>0.8287006191333453</v>
+        <v>0.6148728783572299</v>
       </c>
       <c r="P29">
-        <v>0.8495537779724189</v>
+        <v>0.6561619551121227</v>
+      </c>
+      <c r="Q29">
+        <v>0.6866504972343823</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
         </is>
       </c>
       <c r="B30">
-        <v>0.009379657425210297</v>
+        <v>0</v>
       </c>
       <c r="C30">
-        <v>0.0193453642100857</v>
+        <v>0.002513194363387594</v>
       </c>
       <c r="D30">
-        <v>0.05409405756167451</v>
+        <v>0.009909058892739409</v>
       </c>
       <c r="E30">
-        <v>0.1052627157411438</v>
+        <v>0.05057935826270832</v>
       </c>
       <c r="F30">
-        <v>0.1293365536491764</v>
+        <v>0.07918294043672991</v>
       </c>
       <c r="G30">
-        <v>0.167329671708868</v>
+        <v>0.08721932995420179</v>
       </c>
       <c r="H30">
-        <v>0.3890809299582081</v>
+        <v>0.1185305849164329</v>
       </c>
       <c r="I30">
-        <v>0.5606032711693621</v>
+        <v>0.2188931157213972</v>
       </c>
       <c r="J30">
-        <v>0.5954239970409331</v>
+        <v>0.2531103289527175</v>
       </c>
       <c r="K30">
-        <v>0.684299342680986</v>
+        <v>0.3069414136815398</v>
       </c>
       <c r="L30">
-        <v>0.7356773952780695</v>
+        <v>0.4686284805856903</v>
       </c>
       <c r="M30">
-        <v>0.804427680120105</v>
+        <v>0.5247501113722486</v>
       </c>
       <c r="N30">
-        <v>0.8366182265606904</v>
+        <v>0.5508688625782157</v>
       </c>
       <c r="O30">
-        <v>0.8544506633820679</v>
+        <v>0.6081686862191172</v>
       </c>
       <c r="P30">
-        <v>0.8806313992206468</v>
+        <v>0.6510343857455896</v>
+      </c>
+      <c r="Q30">
+        <v>0.6818357482776825</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
         </is>
       </c>
       <c r="B31">
-        <v>0.008663746054376253</v>
+        <v>0</v>
       </c>
       <c r="C31">
-        <v>0.01790862727689124</v>
+        <v>0.002460880277321831</v>
       </c>
       <c r="D31">
-        <v>0.04912101592766061</v>
+        <v>0.009715751583561971</v>
       </c>
       <c r="E31">
-        <v>0.08995385948217316</v>
+        <v>0.04955177481350148</v>
       </c>
       <c r="F31">
-        <v>0.1084414796356123</v>
+        <v>0.07649585570618433</v>
       </c>
       <c r="G31">
-        <v>0.1318609985903132</v>
+        <v>0.08518564616134028</v>
       </c>
       <c r="H31">
-        <v>0.2604308968032154</v>
+        <v>0.1149236838504777</v>
       </c>
       <c r="I31">
-        <v>0.3898231669347061</v>
+        <v>0.2007159596179308</v>
       </c>
       <c r="J31">
-        <v>0.4288997636972938</v>
+        <v>0.2379442727777523</v>
       </c>
       <c r="K31">
-        <v>0.5422676701469101</v>
+        <v>0.2933050824326722</v>
       </c>
       <c r="L31">
-        <v>0.5830295836208024</v>
+        <v>0.4391503470002153</v>
       </c>
       <c r="M31">
-        <v>0.6641625139608072</v>
+        <v>0.5071654425315706</v>
       </c>
       <c r="N31">
-        <v>0.6835953149612962</v>
+        <v>0.5317370698024697</v>
       </c>
       <c r="O31">
-        <v>0.7006253775788595</v>
+        <v>0.5944436450781108</v>
       </c>
       <c r="P31">
-        <v>0.7196146874275037</v>
+        <v>0.6406983656925949</v>
+      </c>
+      <c r="Q31">
+        <v>0.6746668319758055</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
         </is>
       </c>
       <c r="B32">
-        <v>0.002543824757351376</v>
+        <v>0</v>
       </c>
       <c r="C32">
-        <v>0.009986620336946972</v>
+        <v>0.002596651443072306</v>
       </c>
       <c r="D32">
-        <v>0.05133917070049843</v>
+        <v>0.01021745671489294</v>
       </c>
       <c r="E32">
-        <v>0.08069752145753706</v>
+        <v>0.05279771436849356</v>
       </c>
       <c r="F32">
-        <v>0.08850139590244055</v>
+        <v>0.08393275898225638</v>
       </c>
       <c r="G32">
-        <v>0.1207676715205502</v>
+        <v>0.09191684246749388</v>
       </c>
       <c r="H32">
-        <v>0.2343030907602058</v>
+        <v>0.1268213238953272</v>
       </c>
       <c r="I32">
-        <v>0.2642238096513811</v>
+        <v>0.2540971370653549</v>
       </c>
       <c r="J32">
-        <v>0.3159435952919578</v>
+        <v>0.2832745985411904</v>
       </c>
       <c r="K32">
-        <v>0.495970896123344</v>
+        <v>0.3357134035238354</v>
       </c>
       <c r="L32">
-        <v>0.5400096763014913</v>
+        <v>0.5204341512075827</v>
       </c>
       <c r="M32">
-        <v>0.5662339999232379</v>
+        <v>0.5638231646795602</v>
       </c>
       <c r="N32">
-        <v>0.6184832194275695</v>
+        <v>0.5942931242303621</v>
       </c>
       <c r="O32">
-        <v>0.6592048267960624</v>
+        <v>0.6471144136019888</v>
       </c>
       <c r="P32">
-        <v>0.6893994512225363</v>
+        <v>0.6873004719185891</v>
+      </c>
+      <c r="Q32">
+        <v>0.7269026026183251</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
         </is>
       </c>
       <c r="B33">
-        <v>0.002542672537104607</v>
+        <v>0</v>
       </c>
       <c r="C33">
-        <v>0.0100285831785174</v>
+        <v>0.00258143525573451</v>
       </c>
       <c r="D33">
-        <v>0.05125561435964099</v>
+        <v>0.01014897219805566</v>
       </c>
       <c r="E33">
-        <v>0.08084902466812893</v>
+        <v>0.05228885259468519</v>
       </c>
       <c r="F33">
-        <v>0.08863527390089143</v>
+        <v>0.08276715793586298</v>
       </c>
       <c r="G33">
-        <v>0.1209152033161167</v>
+        <v>0.09062501545994506</v>
       </c>
       <c r="H33">
-        <v>0.22756556642152</v>
+        <v>0.1244057581518299</v>
       </c>
       <c r="I33">
-        <v>0.2604012424915528</v>
+        <v>0.2453284078213062</v>
       </c>
       <c r="J33">
-        <v>0.3130840107676994</v>
+        <v>0.2740878360436966</v>
       </c>
       <c r="K33">
-        <v>0.4801808112663148</v>
+        <v>0.3253546650780698</v>
       </c>
       <c r="L33">
-        <v>0.5329007002870112</v>
+        <v>0.5097946963226545</v>
       </c>
       <c r="M33">
-        <v>0.560322615683525</v>
+        <v>0.5551004816377425</v>
       </c>
       <c r="N33">
-        <v>0.6148728783572299</v>
+        <v>0.5850851867943014</v>
       </c>
       <c r="O33">
-        <v>0.6561619551121227</v>
+        <v>0.6356356901597378</v>
       </c>
       <c r="P33">
-        <v>0.6866504972343823</v>
+        <v>0.6757704600621934</v>
+      </c>
+      <c r="Q33">
+        <v>0.7150310580861374</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
         </is>
       </c>
       <c r="B34">
-        <v>0.002513194363387594</v>
+        <v>0</v>
       </c>
       <c r="C34">
-        <v>0.009909058892739409</v>
+        <v>0.002571683213422271</v>
       </c>
       <c r="D34">
-        <v>0.05057935826270832</v>
+        <v>0.01010924658501899</v>
       </c>
       <c r="E34">
-        <v>0.07918294043672991</v>
+        <v>0.05190555249240492</v>
       </c>
       <c r="F34">
-        <v>0.08721932995420179</v>
+        <v>0.08199353697944978</v>
       </c>
       <c r="G34">
-        <v>0.1185305849164329</v>
+        <v>0.08976997517958796</v>
       </c>
       <c r="H34">
-        <v>0.2188931157213972</v>
+        <v>0.1227607192859574</v>
       </c>
       <c r="I34">
-        <v>0.2531103289527175</v>
+        <v>0.237147949680536</v>
       </c>
       <c r="J34">
-        <v>0.3069414136815398</v>
+        <v>0.2655348122967826</v>
       </c>
       <c r="K34">
-        <v>0.4686284805856903</v>
+        <v>0.3156508205518319</v>
       </c>
       <c r="L34">
-        <v>0.5247501113722486</v>
+        <v>0.5002150735894721</v>
       </c>
       <c r="M34">
-        <v>0.5508688625782157</v>
+        <v>0.54787373655514</v>
       </c>
       <c r="N34">
-        <v>0.6081686862191172</v>
+        <v>0.5765629983355629</v>
       </c>
       <c r="O34">
-        <v>0.6510343857455896</v>
+        <v>0.6257112344300404</v>
       </c>
       <c r="P34">
-        <v>0.6818357482776825</v>
+        <v>0.6644859035624466</v>
+      </c>
+      <c r="Q34">
+        <v>0.7000454976853669</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
         </is>
       </c>
       <c r="B35">
-        <v>0.002460880277321831</v>
+        <v>0</v>
       </c>
       <c r="C35">
-        <v>0.009715751583561971</v>
+        <v>0.002562321090405217</v>
       </c>
       <c r="D35">
-        <v>0.04955177481350148</v>
+        <v>0.01007696120751611</v>
       </c>
       <c r="E35">
-        <v>0.07649585570618433</v>
+        <v>0.05156584390237096</v>
       </c>
       <c r="F35">
-        <v>0.08518564616134028</v>
+        <v>0.08132148375998405</v>
       </c>
       <c r="G35">
-        <v>0.1149236838504777</v>
+        <v>0.08915809868820168</v>
       </c>
       <c r="H35">
-        <v>0.2007159596179308</v>
+        <v>0.1217236151494296</v>
       </c>
       <c r="I35">
-        <v>0.2379442727777523</v>
+        <v>0.231585870803885</v>
       </c>
       <c r="J35">
-        <v>0.2933050824326722</v>
+        <v>0.2605845654807021</v>
       </c>
       <c r="K35">
-        <v>0.4391503470002153</v>
+        <v>0.3103784221256803</v>
       </c>
       <c r="L35">
-        <v>0.5071654425315706</v>
+        <v>0.4917857326361688</v>
       </c>
       <c r="M35">
-        <v>0.5317370698024697</v>
+        <v>0.5414781668361766</v>
       </c>
       <c r="N35">
-        <v>0.5944436450781108</v>
+        <v>0.5685622205244408</v>
       </c>
       <c r="O35">
-        <v>0.6406983656925949</v>
+        <v>0.6161710064366734</v>
       </c>
       <c r="P35">
-        <v>0.6746668319758055</v>
+        <v>0.6548850341503227</v>
+      </c>
+      <c r="Q35">
+        <v>0.6870691402468838</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
         </is>
       </c>
       <c r="B36">
-        <v>0.002596651443072306</v>
+        <v>0</v>
       </c>
       <c r="C36">
-        <v>0.01021745671489294</v>
+        <v>0.002509386633903432</v>
       </c>
       <c r="D36">
-        <v>0.05279771436849356</v>
+        <v>0.009953036614735344</v>
       </c>
       <c r="E36">
-        <v>0.08393275898225638</v>
+        <v>0.05030368797365536</v>
       </c>
       <c r="F36">
-        <v>0.09191684246749388</v>
+        <v>0.07915443524913457</v>
       </c>
       <c r="G36">
-        <v>0.1268213238953272</v>
+        <v>0.08739882409183652</v>
       </c>
       <c r="H36">
-        <v>0.2540971370653549</v>
+        <v>0.1186092115049416</v>
       </c>
       <c r="I36">
-        <v>0.2832745985411904</v>
+        <v>0.2028910476658313</v>
       </c>
       <c r="J36">
-        <v>0.3357134035238354</v>
+        <v>0.2412517349665775</v>
       </c>
       <c r="K36">
-        <v>0.5204341512075827</v>
+        <v>0.2940853769534842</v>
       </c>
       <c r="L36">
-        <v>0.5638231646795602</v>
+        <v>0.4294743198190442</v>
       </c>
       <c r="M36">
-        <v>0.5942931242303621</v>
+        <v>0.5052248501482446</v>
       </c>
       <c r="N36">
-        <v>0.6471144136019888</v>
+        <v>0.533453545276295</v>
       </c>
       <c r="O36">
-        <v>0.6873004719185891</v>
+        <v>0.5893732048292764</v>
       </c>
       <c r="P36">
-        <v>0.7269026026183251</v>
+        <v>0.6349884087415615</v>
+      </c>
+      <c r="Q36">
+        <v>0.6738571492192906</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
         </is>
       </c>
       <c r="B37">
-        <v>0.00258143525573451</v>
+        <v>0</v>
       </c>
       <c r="C37">
-        <v>0.01014897219805566</v>
+        <v>0.03631357773237587</v>
       </c>
       <c r="D37">
-        <v>0.05228885259468519</v>
+        <v>0.1520189530634142</v>
       </c>
       <c r="E37">
-        <v>0.08276715793586298</v>
+        <v>0.1786254179459398</v>
       </c>
       <c r="F37">
-        <v>0.09062501545994506</v>
+        <v>0.2944881820031472</v>
       </c>
       <c r="G37">
-        <v>0.1244057581518299</v>
+        <v>0.4383324151670811</v>
       </c>
       <c r="H37">
-        <v>0.2453284078213062</v>
+        <v>0.5204849831588543</v>
       </c>
       <c r="I37">
-        <v>0.2740878360436966</v>
+        <v>0.6272670040467765</v>
       </c>
       <c r="J37">
-        <v>0.3253546650780698</v>
+        <v>0.6587316524580055</v>
       </c>
       <c r="K37">
-        <v>0.5097946963226545</v>
+        <v>0.6928474594429024</v>
       </c>
       <c r="L37">
-        <v>0.5551004816377425</v>
+        <v>0.7529398435855832</v>
       </c>
       <c r="M37">
-        <v>0.5850851867943014</v>
+        <v>0.7908321827973697</v>
       </c>
       <c r="N37">
-        <v>0.6356356901597378</v>
+        <v>0.8185242123496981</v>
       </c>
       <c r="O37">
-        <v>0.6757704600621934</v>
+        <v>0.8486802892120542</v>
       </c>
       <c r="P37">
-        <v>0.7150310580861374</v>
+        <v>0.8668502740998532</v>
+      </c>
+      <c r="Q37">
+        <v>0.8773637086704661</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
         </is>
       </c>
       <c r="B38">
-        <v>0.002571683213422271</v>
+        <v>0</v>
       </c>
       <c r="C38">
-        <v>0.01010924658501899</v>
+        <v>0.0107406007999149</v>
       </c>
       <c r="D38">
-        <v>0.05190555249240492</v>
+        <v>0.07718364401649136</v>
       </c>
       <c r="E38">
-        <v>0.08199353697944978</v>
+        <v>0.106882498117478</v>
       </c>
       <c r="F38">
-        <v>0.08976997517958796</v>
+        <v>0.2822985029153213</v>
       </c>
       <c r="G38">
-        <v>0.1227607192859574</v>
+        <v>0.4858617979015514</v>
       </c>
       <c r="H38">
-        <v>0.237147949680536</v>
+        <v>0.5114751405775093</v>
       </c>
       <c r="I38">
-        <v>0.2655348122967826</v>
+        <v>0.5494242864175134</v>
       </c>
       <c r="J38">
-        <v>0.3156508205518319</v>
+        <v>0.5993114344465342</v>
       </c>
       <c r="K38">
-        <v>0.5002150735894721</v>
+        <v>0.6301171977253086</v>
       </c>
       <c r="L38">
-        <v>0.54787373655514</v>
+        <v>0.6603611822661544</v>
       </c>
       <c r="M38">
-        <v>0.5765629983355629</v>
+        <v>0.7054540008024308</v>
       </c>
       <c r="N38">
-        <v>0.6257112344300404</v>
+        <v>0.7352868311053065</v>
       </c>
       <c r="O38">
-        <v>0.6644859035624466</v>
+        <v>0.7796785438795589</v>
       </c>
       <c r="P38">
-        <v>0.7000454976853669</v>
+        <v>0.8194571520977163</v>
+      </c>
+      <c r="Q38">
+        <v>0.8425803239991663</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
         </is>
       </c>
       <c r="B39">
-        <v>0.002562321090405217</v>
+        <v>0</v>
       </c>
       <c r="C39">
-        <v>0.01007696120751611</v>
+        <v>0.01224839444641346</v>
       </c>
       <c r="D39">
-        <v>0.05156584390237096</v>
+        <v>0.07246795699831365</v>
       </c>
       <c r="E39">
-        <v>0.08132148375998405</v>
+        <v>0.1022205613853256</v>
       </c>
       <c r="F39">
-        <v>0.08915809868820168</v>
+        <v>0.2226389966208534</v>
       </c>
       <c r="G39">
-        <v>0.1217236151494296</v>
+        <v>0.3560089677224685</v>
       </c>
       <c r="H39">
-        <v>0.231585870803885</v>
+        <v>0.3970952362821796</v>
       </c>
       <c r="I39">
-        <v>0.2605845654807021</v>
+        <v>0.5047884805489242</v>
       </c>
       <c r="J39">
-        <v>0.3103784221256803</v>
+        <v>0.5446745513671065</v>
       </c>
       <c r="K39">
-        <v>0.4917857326361688</v>
+        <v>0.6037132800326879</v>
       </c>
       <c r="L39">
-        <v>0.5414781668361766</v>
+        <v>0.6237435648768161</v>
       </c>
       <c r="M39">
-        <v>0.5685622205244408</v>
+        <v>0.6627677396535731</v>
       </c>
       <c r="N39">
-        <v>0.6161710064366734</v>
+        <v>0.6894414907362796</v>
       </c>
       <c r="O39">
-        <v>0.6548850341503227</v>
+        <v>0.7357169335549638</v>
       </c>
       <c r="P39">
-        <v>0.6870691402468838</v>
+        <v>0.7700789919466354</v>
+      </c>
+      <c r="Q39">
+        <v>0.8059523122879403</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
         </is>
       </c>
       <c r="B40">
-        <v>0.002509386633903432</v>
+        <v>0</v>
       </c>
       <c r="C40">
-        <v>0.009953036614735344</v>
+        <v>0.02630417099022586</v>
       </c>
       <c r="D40">
-        <v>0.05030368797365536</v>
+        <v>0.05260608035904146</v>
       </c>
       <c r="E40">
-        <v>0.07915443524913457</v>
+        <v>0.2020703846161708</v>
       </c>
       <c r="F40">
-        <v>0.08739882409183652</v>
+        <v>0.2417112121974203</v>
       </c>
       <c r="G40">
-        <v>0.1186092115049416</v>
+        <v>0.4628603192951343</v>
       </c>
       <c r="H40">
-        <v>0.2028910476658313</v>
+        <v>0.5329846983481893</v>
       </c>
       <c r="I40">
-        <v>0.2412517349665775</v>
+        <v>0.6037970420328931</v>
       </c>
       <c r="J40">
-        <v>0.2940853769534842</v>
+        <v>0.6619419118304641</v>
       </c>
       <c r="K40">
-        <v>0.4294743198190442</v>
+        <v>0.721043637659341</v>
       </c>
       <c r="L40">
-        <v>0.5052248501482446</v>
+        <v>0.7713308695174464</v>
       </c>
       <c r="M40">
-        <v>0.533453545276295</v>
+        <v>0.792721924329597</v>
       </c>
       <c r="N40">
-        <v>0.5893732048292764</v>
+        <v>0.8142059041303132</v>
       </c>
       <c r="O40">
-        <v>0.6349884087415615</v>
+        <v>0.8347644974542388</v>
       </c>
       <c r="P40">
-        <v>0.6738571492192906</v>
+        <v>0.8516960570938922</v>
+      </c>
+      <c r="Q40">
+        <v>0.8710790957355343</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+          <t>adj_snv_sder_c(1,3,5)_</t>
         </is>
       </c>
       <c r="B41">
-        <v>0.03631357773237587</v>
+        <v>0</v>
       </c>
       <c r="C41">
-        <v>0.1520189530634142</v>
+        <v>0.05362802275242029</v>
       </c>
       <c r="D41">
-        <v>0.1786254179459398</v>
+        <v>0.2200556983661307</v>
       </c>
       <c r="E41">
-        <v>0.2944881820031472</v>
+        <v>0.309544042863932</v>
       </c>
       <c r="F41">
-        <v>0.4383324151670811</v>
+        <v>0.4001592124102217</v>
       </c>
       <c r="G41">
-        <v>0.5204849831588543</v>
+        <v>0.5110008638810387</v>
       </c>
       <c r="H41">
-        <v>0.6272670040467765</v>
+        <v>0.5610105339301721</v>
       </c>
       <c r="I41">
-        <v>0.6587316524580055</v>
+        <v>0.625688988665563</v>
       </c>
       <c r="J41">
-        <v>0.6928474594429024</v>
+        <v>0.6744849580469232</v>
       </c>
       <c r="K41">
-        <v>0.7529398435855832</v>
+        <v>0.7081933019789033</v>
       </c>
       <c r="L41">
-        <v>0.7908321827973697</v>
+        <v>0.7403355567445029</v>
       </c>
       <c r="M41">
-        <v>0.8185242123496981</v>
+        <v>0.7752745495214113</v>
       </c>
       <c r="N41">
-        <v>0.8486802892120542</v>
+        <v>0.8153325684551109</v>
       </c>
       <c r="O41">
-        <v>0.8668502740998532</v>
+        <v>0.8406017519974904</v>
       </c>
       <c r="P41">
-        <v>0.8773637086704661</v>
+        <v>0.862247146522235</v>
+      </c>
+      <c r="Q41">
+        <v>0.8823134450544118</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
+          <t>adj_snv_sder_c(2,3,15)_</t>
         </is>
       </c>
       <c r="B42">
-        <v>0.0107406007999149</v>
+        <v>0</v>
       </c>
       <c r="C42">
-        <v>0.07718364401649136</v>
+        <v>0.0384130121027757</v>
       </c>
       <c r="D42">
-        <v>0.106882498117478</v>
+        <v>0.3070871381670566</v>
       </c>
       <c r="E42">
-        <v>0.2822985029153213</v>
+        <v>0.3699993999528992</v>
       </c>
       <c r="F42">
-        <v>0.4858617979015514</v>
+        <v>0.4815049079877678</v>
       </c>
       <c r="G42">
-        <v>0.5114751405775093</v>
+        <v>0.544224892100877</v>
       </c>
       <c r="H42">
-        <v>0.5494242864175134</v>
+        <v>0.6189282298273389</v>
       </c>
       <c r="I42">
-        <v>0.5993114344465342</v>
+        <v>0.6785561556613604</v>
       </c>
       <c r="J42">
-        <v>0.6301171977253086</v>
+        <v>0.7149168262333748</v>
       </c>
       <c r="K42">
-        <v>0.6603611822661544</v>
+        <v>0.7457651400167102</v>
       </c>
       <c r="L42">
-        <v>0.7054540008024308</v>
+        <v>0.7867740198230747</v>
       </c>
       <c r="M42">
-        <v>0.7352868311053065</v>
+        <v>0.814175904437616</v>
       </c>
       <c r="N42">
-        <v>0.7796785438795589</v>
+        <v>0.8575930151879002</v>
       </c>
       <c r="O42">
-        <v>0.8194571520977163</v>
+        <v>0.880664804844596</v>
       </c>
       <c r="P42">
-        <v>0.8425803239991663</v>
+        <v>0.8940453769198531</v>
+      </c>
+      <c r="Q42">
+        <v>0.9181086367245604</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+          <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
         </is>
       </c>
       <c r="B43">
-        <v>0.01224839444641346</v>
+        <v>0</v>
       </c>
       <c r="C43">
-        <v>0.07246795699831365</v>
+        <v>0.03103074304490128</v>
       </c>
       <c r="D43">
-        <v>0.1022205613853256</v>
+        <v>0.1243888064224506</v>
       </c>
       <c r="E43">
-        <v>0.2226389966208534</v>
+        <v>0.3578139561512588</v>
       </c>
       <c r="F43">
-        <v>0.3560089677224685</v>
+        <v>0.47116190938766</v>
       </c>
       <c r="G43">
-        <v>0.3970952362821796</v>
+        <v>0.5331274565750248</v>
       </c>
       <c r="H43">
-        <v>0.5047884805489242</v>
+        <v>0.5876706426852913</v>
       </c>
       <c r="I43">
-        <v>0.5446745513671065</v>
+        <v>0.6574705259016818</v>
       </c>
       <c r="J43">
-        <v>0.6037132800326879</v>
+        <v>0.6955646135346252</v>
       </c>
       <c r="K43">
-        <v>0.6237435648768161</v>
+        <v>0.7585301926271285</v>
       </c>
       <c r="L43">
-        <v>0.6627677396535731</v>
+        <v>0.7986975672684995</v>
       </c>
       <c r="M43">
-        <v>0.6894414907362796</v>
+        <v>0.8271970173643288</v>
       </c>
       <c r="N43">
-        <v>0.7357169335549638</v>
+        <v>0.8551543508421189</v>
       </c>
       <c r="O43">
-        <v>0.7700789919466354</v>
+        <v>0.8760788149359741</v>
       </c>
       <c r="P43">
-        <v>0.8059523122879403</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
-        </is>
-      </c>
-      <c r="B44">
-        <v>0.02630417099022586</v>
-      </c>
-      <c r="C44">
-        <v>0.05260608035904146</v>
-      </c>
-      <c r="D44">
-        <v>0.2020703846161708</v>
-      </c>
-      <c r="E44">
-        <v>0.2417112121974203</v>
-      </c>
-      <c r="F44">
-        <v>0.4628603192951343</v>
-      </c>
-      <c r="G44">
-        <v>0.5329846983481893</v>
-      </c>
-      <c r="H44">
-        <v>0.6037970420328931</v>
-      </c>
-      <c r="I44">
-        <v>0.6619419118304641</v>
-      </c>
-      <c r="J44">
-        <v>0.721043637659341</v>
-      </c>
-      <c r="K44">
-        <v>0.7713308695174464</v>
-      </c>
-      <c r="L44">
-        <v>0.792721924329597</v>
-      </c>
-      <c r="M44">
-        <v>0.8142059041303132</v>
-      </c>
-      <c r="N44">
-        <v>0.8347644974542388</v>
-      </c>
-      <c r="O44">
-        <v>0.8516960570938922</v>
-      </c>
-      <c r="P44">
-        <v>0.8710790957355343</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>adj_snv_sder_c(1,3,5)_</t>
-        </is>
-      </c>
-      <c r="B45">
-        <v>0.05362802275242029</v>
-      </c>
-      <c r="C45">
-        <v>0.2200556983661307</v>
-      </c>
-      <c r="D45">
-        <v>0.309544042863932</v>
-      </c>
-      <c r="E45">
-        <v>0.4001592124102217</v>
-      </c>
-      <c r="F45">
-        <v>0.5110008638810387</v>
-      </c>
-      <c r="G45">
-        <v>0.5610105339301721</v>
-      </c>
-      <c r="H45">
-        <v>0.625688988665563</v>
-      </c>
-      <c r="I45">
-        <v>0.6744849580469232</v>
-      </c>
-      <c r="J45">
-        <v>0.7081933019789033</v>
-      </c>
-      <c r="K45">
-        <v>0.7403355567445029</v>
-      </c>
-      <c r="L45">
-        <v>0.7752745495214113</v>
-      </c>
-      <c r="M45">
-        <v>0.8153325684551109</v>
-      </c>
-      <c r="N45">
-        <v>0.8406017519974904</v>
-      </c>
-      <c r="O45">
-        <v>0.862247146522235</v>
-      </c>
-      <c r="P45">
-        <v>0.8823134450544118</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>adj_snv_sder_c(2,3,15)_</t>
-        </is>
-      </c>
-      <c r="B46">
-        <v>0.0384130121027757</v>
-      </c>
-      <c r="C46">
-        <v>0.3070871381670566</v>
-      </c>
-      <c r="D46">
-        <v>0.3699993999528992</v>
-      </c>
-      <c r="E46">
-        <v>0.4815049079877678</v>
-      </c>
-      <c r="F46">
-        <v>0.544224892100877</v>
-      </c>
-      <c r="G46">
-        <v>0.6189282298273389</v>
-      </c>
-      <c r="H46">
-        <v>0.6785561556613604</v>
-      </c>
-      <c r="I46">
-        <v>0.7149168262333748</v>
-      </c>
-      <c r="J46">
-        <v>0.7457651400167102</v>
-      </c>
-      <c r="K46">
-        <v>0.7867740198230747</v>
-      </c>
-      <c r="L46">
-        <v>0.814175904437616</v>
-      </c>
-      <c r="M46">
-        <v>0.8575930151879002</v>
-      </c>
-      <c r="N46">
-        <v>0.880664804844596</v>
-      </c>
-      <c r="O46">
-        <v>0.8940453769198531</v>
-      </c>
-      <c r="P46">
-        <v>0.9181086367245604</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
-        </is>
-      </c>
-      <c r="B47">
-        <v>0.03103074304490128</v>
-      </c>
-      <c r="C47">
-        <v>0.1243888064224506</v>
-      </c>
-      <c r="D47">
-        <v>0.3578139561512588</v>
-      </c>
-      <c r="E47">
-        <v>0.47116190938766</v>
-      </c>
-      <c r="F47">
-        <v>0.5331274565750248</v>
-      </c>
-      <c r="G47">
-        <v>0.5876706426852913</v>
-      </c>
-      <c r="H47">
-        <v>0.6574705259016818</v>
-      </c>
-      <c r="I47">
-        <v>0.6955646135346252</v>
-      </c>
-      <c r="J47">
-        <v>0.7585301926271285</v>
-      </c>
-      <c r="K47">
-        <v>0.7986975672684995</v>
-      </c>
-      <c r="L47">
-        <v>0.8271970173643288</v>
-      </c>
-      <c r="M47">
-        <v>0.8551543508421189</v>
-      </c>
-      <c r="N47">
-        <v>0.8760788149359741</v>
-      </c>
-      <c r="O47">
         <v>0.8907410957874282</v>
       </c>
-      <c r="P47">
+      <c r="Q43">
         <v>0.904670112247317</v>
       </c>
     </row>
